--- a/bioinfo_revision/simulation_results/tables/gmac/by_sample_size/gmac_gmac_n1000.xlsx
+++ b/bioinfo_revision/simulation_results/tables/gmac/by_sample_size/gmac_gmac_n1000.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:19</t>
+          <t>2026-08-27 19:53:39</t>
         </is>
       </c>
     </row>

--- a/bioinfo_revision/simulation_results/tables/gmac/by_sample_size/gmac_gmac_n1000.xlsx
+++ b/bioinfo_revision/simulation_results/tables/gmac/by_sample_size/gmac_gmac_n1000.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:53:39</t>
+          <t>2026-08-27 23:10:27</t>
         </is>
       </c>
     </row>
